--- a/ML & Data analytics projects/Bike Rental Analysis & Prediction_project/data for test.xlsx
+++ b/ML & Data analytics projects/Bike Rental Analysis & Prediction_project/data for test.xlsx
@@ -8,17 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RPC\Desktop\jupyter files\1-ML &amp; Data Science projects-github\ML &amp; Data analytics projects\Bike Rental Analysis &amp; Prediction_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC695AE-742E-473F-8821-0DA8E5CDF940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63A27571-069E-4E42-9D5E-B76D55936659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -28,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="41">
   <si>
     <t>Winter</t>
   </si>
@@ -40,9 +51,6 @@
   </si>
   <si>
     <t>Saturday</t>
-  </si>
-  <si>
-    <t>Weekend</t>
   </si>
   <si>
     <t>Evening</t>
@@ -76,9 +84,6 @@
   </si>
   <si>
     <t>Friday</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t>Midday/Noon</t>
@@ -147,9 +152,6 @@
     <t>day</t>
   </si>
   <si>
-    <t>weekend</t>
-  </si>
-  <si>
     <t>hour</t>
   </si>
   <si>
@@ -158,12 +160,15 @@
   <si>
     <t>weather_feeling</t>
   </si>
+  <si>
+    <t>no</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,6 +180,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -212,11 +225,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -497,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P97"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="17.08984375" customWidth="1"/>
@@ -506,69 +524,66 @@
     <col min="7" max="7" width="14.1796875" customWidth="1"/>
     <col min="8" max="8" width="15.90625" customWidth="1"/>
     <col min="9" max="9" width="17.1796875" customWidth="1"/>
-    <col min="10" max="10" width="10.81640625" customWidth="1"/>
+    <col min="10" max="10" width="10.81640625" style="3" customWidth="1"/>
     <col min="11" max="11" width="10.26953125" customWidth="1"/>
     <col min="12" max="12" width="9.81640625" customWidth="1"/>
-    <col min="15" max="15" width="31.7265625" customWidth="1"/>
-    <col min="16" max="16" width="15.36328125" customWidth="1"/>
+    <col min="14" max="14" width="31.7265625" customWidth="1"/>
+    <col min="15" max="15" width="15.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>0</v>
+      <c r="B2" t="s">
+        <v>40</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -591,7 +606,7 @@
       <c r="I2">
         <v>37</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="3">
         <v>2011</v>
       </c>
       <c r="K2" t="s">
@@ -600,31 +615,28 @@
       <c r="L2" t="s">
         <v>3</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2">
+        <v>19</v>
+      </c>
+      <c r="N2" t="s">
         <v>4</v>
-      </c>
-      <c r="N2">
-        <v>19</v>
       </c>
       <c r="O2" t="s">
         <v>5</v>
       </c>
-      <c r="P2" t="s">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
       </c>
       <c r="E3">
         <v>16.399999999999999</v>
@@ -641,7 +653,7 @@
       <c r="I3">
         <v>36</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="3">
         <v>2011</v>
       </c>
       <c r="K3" t="s">
@@ -650,31 +662,28 @@
       <c r="L3" t="s">
         <v>3</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3">
+        <v>20</v>
+      </c>
+      <c r="N3" t="s">
         <v>4</v>
       </c>
-      <c r="N3">
-        <v>20</v>
-      </c>
       <c r="O3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>0</v>
       </c>
-      <c r="B4">
-        <v>0</v>
+      <c r="B4" t="s">
+        <v>40</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>16.399999999999999</v>
@@ -691,7 +700,7 @@
       <c r="I4">
         <v>34</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="3">
         <v>2011</v>
       </c>
       <c r="K4" t="s">
@@ -700,31 +709,28 @@
       <c r="L4" t="s">
         <v>3</v>
       </c>
-      <c r="M4" t="s">
-        <v>4</v>
-      </c>
-      <c r="N4">
+      <c r="M4">
         <v>21</v>
       </c>
+      <c r="N4" t="s">
+        <v>8</v>
+      </c>
       <c r="O4" t="s">
-        <v>9</v>
-      </c>
-      <c r="P4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>0</v>
       </c>
-      <c r="B5">
-        <v>0</v>
+      <c r="B5" t="s">
+        <v>40</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>16.399999999999999</v>
@@ -741,7 +747,7 @@
       <c r="I5">
         <v>28</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="3">
         <v>2011</v>
       </c>
       <c r="K5" t="s">
@@ -750,31 +756,28 @@
       <c r="L5" t="s">
         <v>3</v>
       </c>
-      <c r="M5" t="s">
-        <v>4</v>
-      </c>
-      <c r="N5">
+      <c r="M5">
         <v>22</v>
       </c>
+      <c r="N5" t="s">
+        <v>8</v>
+      </c>
       <c r="O5" t="s">
-        <v>9</v>
-      </c>
-      <c r="P5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>0</v>
       </c>
-      <c r="B6">
-        <v>0</v>
+      <c r="B6" t="s">
+        <v>40</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>18.86</v>
@@ -791,7 +794,7 @@
       <c r="I6">
         <v>39</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="3">
         <v>2011</v>
       </c>
       <c r="K6" t="s">
@@ -800,31 +803,28 @@
       <c r="L6" t="s">
         <v>3</v>
       </c>
-      <c r="M6" t="s">
-        <v>4</v>
-      </c>
-      <c r="N6">
+      <c r="M6">
         <v>23</v>
       </c>
+      <c r="N6" t="s">
+        <v>8</v>
+      </c>
       <c r="O6" t="s">
-        <v>9</v>
-      </c>
-      <c r="P6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7" t="s">
-        <v>7</v>
       </c>
       <c r="E7">
         <v>18.86</v>
@@ -841,40 +841,37 @@
       <c r="I7">
         <v>17</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="3">
         <v>2011</v>
       </c>
       <c r="K7" t="s">
         <v>2</v>
       </c>
       <c r="L7" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
         <v>10</v>
       </c>
-      <c r="M7" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
       <c r="O7" t="s">
-        <v>11</v>
-      </c>
-      <c r="P7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8" t="s">
-        <v>7</v>
       </c>
       <c r="E8">
         <v>18.04</v>
@@ -891,40 +888,37 @@
       <c r="I8">
         <v>17</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="3">
         <v>2011</v>
       </c>
       <c r="K8" t="s">
         <v>2</v>
       </c>
       <c r="L8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8" t="s">
         <v>10</v>
       </c>
-      <c r="M8" t="s">
-        <v>4</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
       <c r="O8" t="s">
-        <v>11</v>
-      </c>
-      <c r="P8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9" t="s">
-        <v>7</v>
       </c>
       <c r="E9">
         <v>17.22</v>
@@ -941,40 +935,37 @@
       <c r="I9">
         <v>9</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="3">
         <v>2011</v>
       </c>
       <c r="K9" t="s">
         <v>2</v>
       </c>
       <c r="L9" t="s">
+        <v>9</v>
+      </c>
+      <c r="M9">
+        <v>2</v>
+      </c>
+      <c r="N9" t="s">
         <v>10</v>
       </c>
-      <c r="M9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N9">
-        <v>2</v>
-      </c>
       <c r="O9" t="s">
-        <v>11</v>
-      </c>
-      <c r="P9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10" t="s">
-        <v>7</v>
       </c>
       <c r="E10">
         <v>18.86</v>
@@ -991,40 +982,37 @@
       <c r="I10">
         <v>6</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="3">
         <v>2011</v>
       </c>
       <c r="K10" t="s">
         <v>2</v>
       </c>
       <c r="L10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M10">
+        <v>3</v>
+      </c>
+      <c r="N10" t="s">
         <v>10</v>
       </c>
-      <c r="M10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N10">
-        <v>3</v>
-      </c>
       <c r="O10" t="s">
-        <v>11</v>
-      </c>
-      <c r="P10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11" t="s">
-        <v>7</v>
       </c>
       <c r="E11">
         <v>18.86</v>
@@ -1041,34 +1029,31 @@
       <c r="I11">
         <v>3</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="3">
         <v>2011</v>
       </c>
       <c r="K11" t="s">
         <v>2</v>
       </c>
       <c r="L11" t="s">
+        <v>9</v>
+      </c>
+      <c r="M11">
+        <v>4</v>
+      </c>
+      <c r="N11" t="s">
         <v>10</v>
       </c>
-      <c r="M11" t="s">
-        <v>4</v>
-      </c>
-      <c r="N11">
-        <v>4</v>
-      </c>
       <c r="O11" t="s">
-        <v>11</v>
-      </c>
-      <c r="P11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>0</v>
       </c>
-      <c r="B12">
-        <v>0</v>
+      <c r="B12" t="s">
+        <v>40</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1091,40 +1076,37 @@
       <c r="I12">
         <v>2</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="3">
         <v>2011</v>
       </c>
       <c r="K12" t="s">
         <v>2</v>
       </c>
       <c r="L12" t="s">
-        <v>10</v>
-      </c>
-      <c r="M12" t="s">
-        <v>4</v>
-      </c>
-      <c r="N12">
+        <v>9</v>
+      </c>
+      <c r="M12">
         <v>6</v>
       </c>
+      <c r="N12" t="s">
+        <v>11</v>
+      </c>
       <c r="O12" t="s">
-        <v>12</v>
-      </c>
-      <c r="P12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13" t="s">
-        <v>7</v>
       </c>
       <c r="E13">
         <v>16.399999999999999</v>
@@ -1141,34 +1123,31 @@
       <c r="I13">
         <v>1</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="3">
         <v>2011</v>
       </c>
       <c r="K13" t="s">
         <v>2</v>
       </c>
       <c r="L13" t="s">
-        <v>10</v>
-      </c>
-      <c r="M13" t="s">
-        <v>4</v>
-      </c>
-      <c r="N13">
+        <v>9</v>
+      </c>
+      <c r="M13">
         <v>7</v>
       </c>
+      <c r="N13" t="s">
+        <v>11</v>
+      </c>
       <c r="O13" t="s">
-        <v>12</v>
-      </c>
-      <c r="P13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>0</v>
       </c>
-      <c r="B14">
-        <v>0</v>
+      <c r="B14" t="s">
+        <v>40</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1191,40 +1170,37 @@
       <c r="I14">
         <v>8</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="3">
         <v>2011</v>
       </c>
       <c r="K14" t="s">
         <v>2</v>
       </c>
       <c r="L14" t="s">
-        <v>10</v>
-      </c>
-      <c r="M14" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14">
+        <v>9</v>
+      </c>
+      <c r="M14">
         <v>8</v>
       </c>
+      <c r="N14" t="s">
+        <v>11</v>
+      </c>
       <c r="O14" t="s">
-        <v>12</v>
-      </c>
-      <c r="P14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>0</v>
       </c>
-      <c r="B15">
-        <v>0</v>
+      <c r="B15" t="s">
+        <v>40</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15">
         <v>15.58</v>
@@ -1241,40 +1217,37 @@
       <c r="I15">
         <v>20</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="3">
         <v>2011</v>
       </c>
       <c r="K15" t="s">
         <v>2</v>
       </c>
       <c r="L15" t="s">
-        <v>10</v>
-      </c>
-      <c r="M15" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15">
         <v>9</v>
       </c>
+      <c r="M15">
+        <v>9</v>
+      </c>
+      <c r="N15" t="s">
+        <v>11</v>
+      </c>
       <c r="O15" t="s">
-        <v>12</v>
-      </c>
-      <c r="P15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>0</v>
       </c>
-      <c r="B16">
-        <v>0</v>
+      <c r="B16" t="s">
+        <v>40</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>14.76</v>
@@ -1291,40 +1264,37 @@
       <c r="I16">
         <v>53</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="3">
         <v>2011</v>
       </c>
       <c r="K16" t="s">
         <v>2</v>
       </c>
       <c r="L16" t="s">
+        <v>9</v>
+      </c>
+      <c r="M16">
         <v>10</v>
       </c>
-      <c r="M16" t="s">
-        <v>4</v>
-      </c>
-      <c r="N16">
-        <v>10</v>
+      <c r="N16" t="s">
+        <v>11</v>
       </c>
       <c r="O16" t="s">
-        <v>12</v>
-      </c>
-      <c r="P16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>0</v>
       </c>
-      <c r="B17">
-        <v>0</v>
+      <c r="B17" t="s">
+        <v>40</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17">
         <v>14.76</v>
@@ -1341,40 +1311,37 @@
       <c r="I17">
         <v>70</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="3">
         <v>2011</v>
       </c>
       <c r="K17" t="s">
         <v>2</v>
       </c>
       <c r="L17" t="s">
-        <v>10</v>
-      </c>
-      <c r="M17" t="s">
-        <v>4</v>
-      </c>
-      <c r="N17">
+        <v>9</v>
+      </c>
+      <c r="M17">
         <v>11</v>
       </c>
+      <c r="N17" t="s">
+        <v>11</v>
+      </c>
       <c r="O17" t="s">
-        <v>12</v>
-      </c>
-      <c r="P17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>0</v>
       </c>
-      <c r="B18">
-        <v>0</v>
+      <c r="B18" t="s">
+        <v>40</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E18">
         <v>15.58</v>
@@ -1391,40 +1358,37 @@
       <c r="I18">
         <v>10</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="3">
         <v>2011</v>
       </c>
       <c r="K18" t="s">
+        <v>13</v>
+      </c>
+      <c r="L18" t="s">
         <v>14</v>
       </c>
-      <c r="L18" t="s">
-        <v>15</v>
-      </c>
-      <c r="M18" t="s">
-        <v>16</v>
-      </c>
-      <c r="N18">
+      <c r="M18">
         <v>5</v>
       </c>
+      <c r="N18" t="s">
+        <v>10</v>
+      </c>
       <c r="O18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>0</v>
       </c>
-      <c r="B19">
-        <v>0</v>
+      <c r="B19" t="s">
+        <v>40</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19">
         <v>16.399999999999999</v>
@@ -1441,40 +1405,37 @@
       <c r="I19">
         <v>36</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="3">
         <v>2011</v>
       </c>
       <c r="K19" t="s">
+        <v>13</v>
+      </c>
+      <c r="L19" t="s">
         <v>14</v>
       </c>
-      <c r="L19" t="s">
-        <v>15</v>
-      </c>
-      <c r="M19" t="s">
-        <v>16</v>
-      </c>
-      <c r="N19">
+      <c r="M19">
         <v>6</v>
       </c>
+      <c r="N19" t="s">
+        <v>11</v>
+      </c>
       <c r="O19" t="s">
-        <v>12</v>
-      </c>
-      <c r="P19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>0</v>
       </c>
-      <c r="B20">
-        <v>0</v>
+      <c r="B20" t="s">
+        <v>40</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E20">
         <v>16.399999999999999</v>
@@ -1491,40 +1452,37 @@
       <c r="I20">
         <v>123</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="3">
         <v>2011</v>
       </c>
       <c r="K20" t="s">
+        <v>13</v>
+      </c>
+      <c r="L20" t="s">
         <v>14</v>
       </c>
-      <c r="L20" t="s">
-        <v>15</v>
-      </c>
-      <c r="M20" t="s">
-        <v>16</v>
-      </c>
-      <c r="N20">
+      <c r="M20">
         <v>7</v>
       </c>
+      <c r="N20" t="s">
+        <v>11</v>
+      </c>
       <c r="O20" t="s">
-        <v>12</v>
-      </c>
-      <c r="P20" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>0</v>
       </c>
-      <c r="B21">
-        <v>0</v>
+      <c r="B21" t="s">
+        <v>40</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E21">
         <v>17.22</v>
@@ -1541,40 +1499,37 @@
       <c r="I21">
         <v>280</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="3">
         <v>2011</v>
       </c>
       <c r="K21" t="s">
+        <v>13</v>
+      </c>
+      <c r="L21" t="s">
         <v>14</v>
       </c>
-      <c r="L21" t="s">
-        <v>15</v>
-      </c>
-      <c r="M21" t="s">
-        <v>16</v>
-      </c>
-      <c r="N21">
+      <c r="M21">
         <v>8</v>
       </c>
+      <c r="N21" t="s">
+        <v>11</v>
+      </c>
       <c r="O21" t="s">
-        <v>12</v>
-      </c>
-      <c r="P21" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>0</v>
       </c>
-      <c r="B22">
-        <v>0</v>
+      <c r="B22" t="s">
+        <v>40</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E22">
         <v>18.86</v>
@@ -1591,40 +1546,37 @@
       <c r="I22">
         <v>210</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="3">
         <v>2011</v>
       </c>
       <c r="K22" t="s">
+        <v>13</v>
+      </c>
+      <c r="L22" t="s">
         <v>14</v>
       </c>
-      <c r="L22" t="s">
-        <v>15</v>
-      </c>
-      <c r="M22" t="s">
-        <v>16</v>
-      </c>
-      <c r="N22">
+      <c r="M22">
         <v>9</v>
       </c>
+      <c r="N22" t="s">
+        <v>11</v>
+      </c>
       <c r="O22" t="s">
-        <v>12</v>
-      </c>
-      <c r="P22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>0</v>
       </c>
-      <c r="B23">
-        <v>0</v>
+      <c r="B23" t="s">
+        <v>40</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E23">
         <v>21.32</v>
@@ -1641,40 +1593,37 @@
       <c r="I23">
         <v>117</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="3">
         <v>2011</v>
       </c>
       <c r="K23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L23" t="s">
         <v>14</v>
       </c>
-      <c r="L23" t="s">
-        <v>15</v>
-      </c>
-      <c r="M23" t="s">
-        <v>16</v>
-      </c>
-      <c r="N23">
+      <c r="M23">
         <v>10</v>
       </c>
+      <c r="N23" t="s">
+        <v>11</v>
+      </c>
       <c r="O23" t="s">
-        <v>12</v>
-      </c>
-      <c r="P23" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>0</v>
       </c>
-      <c r="B24">
-        <v>0</v>
+      <c r="B24" t="s">
+        <v>40</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E24">
         <v>22.14</v>
@@ -1691,40 +1640,37 @@
       <c r="I24">
         <v>159</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="3">
         <v>2011</v>
       </c>
       <c r="K24" t="s">
+        <v>13</v>
+      </c>
+      <c r="L24" t="s">
         <v>14</v>
       </c>
-      <c r="L24" t="s">
-        <v>15</v>
-      </c>
-      <c r="M24" t="s">
-        <v>16</v>
-      </c>
-      <c r="N24">
+      <c r="M24">
         <v>11</v>
       </c>
+      <c r="N24" t="s">
+        <v>11</v>
+      </c>
       <c r="O24" t="s">
-        <v>12</v>
-      </c>
-      <c r="P24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25" t="s">
-        <v>7</v>
       </c>
       <c r="E25">
         <v>22.96</v>
@@ -1741,40 +1687,37 @@
       <c r="I25">
         <v>195</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="3">
         <v>2011</v>
       </c>
       <c r="K25" t="s">
+        <v>13</v>
+      </c>
+      <c r="L25" t="s">
         <v>14</v>
       </c>
-      <c r="L25" t="s">
+      <c r="M25">
+        <v>12</v>
+      </c>
+      <c r="N25" t="s">
         <v>15</v>
       </c>
-      <c r="M25" t="s">
+      <c r="O25" t="s">
         <v>16</v>
       </c>
-      <c r="N25">
-        <v>12</v>
-      </c>
-      <c r="O25" t="s">
-        <v>17</v>
-      </c>
-      <c r="P25" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>0</v>
       </c>
-      <c r="B26">
-        <v>0</v>
+      <c r="B26" t="s">
+        <v>40</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E26">
         <v>26.24</v>
@@ -1791,40 +1734,37 @@
       <c r="I26">
         <v>175</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="3">
         <v>2011</v>
       </c>
       <c r="K26" t="s">
+        <v>13</v>
+      </c>
+      <c r="L26" t="s">
         <v>14</v>
       </c>
-      <c r="L26" t="s">
+      <c r="M26">
+        <v>13</v>
+      </c>
+      <c r="N26" t="s">
         <v>15</v>
-      </c>
-      <c r="M26" t="s">
-        <v>16</v>
-      </c>
-      <c r="N26">
-        <v>13</v>
       </c>
       <c r="O26" t="s">
         <v>17</v>
       </c>
-      <c r="P26" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>0</v>
       </c>
-      <c r="B27">
-        <v>0</v>
+      <c r="B27" t="s">
+        <v>40</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E27">
         <v>27.06</v>
@@ -1841,40 +1781,37 @@
       <c r="I27">
         <v>174</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="3">
         <v>2011</v>
       </c>
       <c r="K27" t="s">
+        <v>13</v>
+      </c>
+      <c r="L27" t="s">
         <v>14</v>
       </c>
-      <c r="L27" t="s">
-        <v>15</v>
-      </c>
-      <c r="M27" t="s">
-        <v>16</v>
-      </c>
-      <c r="N27">
+      <c r="M27">
         <v>14</v>
       </c>
+      <c r="N27" t="s">
+        <v>18</v>
+      </c>
       <c r="O27" t="s">
-        <v>20</v>
-      </c>
-      <c r="P27" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>0</v>
       </c>
-      <c r="B28">
-        <v>0</v>
+      <c r="B28" t="s">
+        <v>40</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E28">
         <v>27.88</v>
@@ -1891,40 +1828,37 @@
       <c r="I28">
         <v>173</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="3">
         <v>2011</v>
       </c>
       <c r="K28" t="s">
+        <v>13</v>
+      </c>
+      <c r="L28" t="s">
         <v>14</v>
       </c>
-      <c r="L28" t="s">
+      <c r="M28">
         <v>15</v>
       </c>
-      <c r="M28" t="s">
-        <v>16</v>
-      </c>
-      <c r="N28">
-        <v>15</v>
+      <c r="N28" t="s">
+        <v>18</v>
       </c>
       <c r="O28" t="s">
-        <v>20</v>
-      </c>
-      <c r="P28" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>0</v>
       </c>
-      <c r="B29">
-        <v>0</v>
+      <c r="B29" t="s">
+        <v>40</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E29">
         <v>27.88</v>
@@ -1941,40 +1875,37 @@
       <c r="I29">
         <v>204</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="3">
         <v>2011</v>
       </c>
       <c r="K29" t="s">
+        <v>13</v>
+      </c>
+      <c r="L29" t="s">
         <v>14</v>
       </c>
-      <c r="L29" t="s">
-        <v>15</v>
-      </c>
-      <c r="M29" t="s">
+      <c r="M29">
         <v>16</v>
       </c>
-      <c r="N29">
-        <v>16</v>
+      <c r="N29" t="s">
+        <v>18</v>
       </c>
       <c r="O29" t="s">
-        <v>20</v>
-      </c>
-      <c r="P29" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>0</v>
       </c>
-      <c r="B30">
-        <v>0</v>
+      <c r="B30" t="s">
+        <v>40</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E30">
         <v>28.7</v>
@@ -1991,40 +1922,37 @@
       <c r="I30">
         <v>332</v>
       </c>
-      <c r="J30">
+      <c r="J30" s="3">
         <v>2011</v>
       </c>
       <c r="K30" t="s">
+        <v>13</v>
+      </c>
+      <c r="L30" t="s">
         <v>14</v>
       </c>
-      <c r="L30" t="s">
-        <v>15</v>
-      </c>
-      <c r="M30" t="s">
-        <v>16</v>
-      </c>
-      <c r="N30">
+      <c r="M30">
         <v>17</v>
       </c>
+      <c r="N30" t="s">
+        <v>18</v>
+      </c>
       <c r="O30" t="s">
-        <v>20</v>
-      </c>
-      <c r="P30" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>0</v>
       </c>
-      <c r="B31">
-        <v>0</v>
+      <c r="B31" t="s">
+        <v>40</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E31">
         <v>27.88</v>
@@ -2041,40 +1969,37 @@
       <c r="I31">
         <v>331</v>
       </c>
-      <c r="J31">
+      <c r="J31" s="3">
         <v>2011</v>
       </c>
       <c r="K31" t="s">
+        <v>13</v>
+      </c>
+      <c r="L31" t="s">
         <v>14</v>
       </c>
-      <c r="L31" t="s">
-        <v>15</v>
-      </c>
-      <c r="M31" t="s">
-        <v>16</v>
-      </c>
-      <c r="N31">
+      <c r="M31">
         <v>18</v>
       </c>
+      <c r="N31" t="s">
+        <v>4</v>
+      </c>
       <c r="O31" t="s">
-        <v>5</v>
-      </c>
-      <c r="P31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>0</v>
       </c>
-      <c r="B32">
-        <v>0</v>
+      <c r="B32" t="s">
+        <v>40</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E32">
         <v>27.06</v>
@@ -2091,40 +2016,37 @@
       <c r="I32">
         <v>190</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="3">
         <v>2011</v>
       </c>
       <c r="K32" t="s">
+        <v>13</v>
+      </c>
+      <c r="L32" t="s">
         <v>14</v>
       </c>
-      <c r="L32" t="s">
-        <v>15</v>
-      </c>
-      <c r="M32" t="s">
-        <v>16</v>
-      </c>
-      <c r="N32">
+      <c r="M32">
         <v>19</v>
       </c>
+      <c r="N32" t="s">
+        <v>4</v>
+      </c>
       <c r="O32" t="s">
-        <v>5</v>
-      </c>
-      <c r="P32" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>0</v>
       </c>
-      <c r="B33">
-        <v>0</v>
+      <c r="B33" t="s">
+        <v>40</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E33">
         <v>25.42</v>
@@ -2141,40 +2063,37 @@
       <c r="I33">
         <v>149</v>
       </c>
-      <c r="J33">
+      <c r="J33" s="3">
         <v>2011</v>
       </c>
       <c r="K33" t="s">
+        <v>13</v>
+      </c>
+      <c r="L33" t="s">
         <v>14</v>
       </c>
-      <c r="L33" t="s">
-        <v>15</v>
-      </c>
-      <c r="M33" t="s">
-        <v>16</v>
-      </c>
-      <c r="N33">
+      <c r="M33">
         <v>20</v>
       </c>
+      <c r="N33" t="s">
+        <v>4</v>
+      </c>
       <c r="O33" t="s">
-        <v>5</v>
-      </c>
-      <c r="P33" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>0</v>
       </c>
-      <c r="B34">
-        <v>0</v>
+      <c r="B34" t="s">
+        <v>40</v>
       </c>
       <c r="C34">
         <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E34">
         <v>25.42</v>
@@ -2191,40 +2110,37 @@
       <c r="I34">
         <v>113</v>
       </c>
-      <c r="J34">
+      <c r="J34" s="3">
         <v>2011</v>
       </c>
       <c r="K34" t="s">
+        <v>13</v>
+      </c>
+      <c r="L34" t="s">
         <v>14</v>
       </c>
-      <c r="L34" t="s">
-        <v>15</v>
-      </c>
-      <c r="M34" t="s">
-        <v>16</v>
-      </c>
-      <c r="N34">
+      <c r="M34">
         <v>21</v>
       </c>
+      <c r="N34" t="s">
+        <v>8</v>
+      </c>
       <c r="O34" t="s">
-        <v>9</v>
-      </c>
-      <c r="P34" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>0</v>
       </c>
-      <c r="B35">
-        <v>0</v>
+      <c r="B35" t="s">
+        <v>40</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E35">
         <v>25.42</v>
@@ -2241,40 +2157,37 @@
       <c r="I35">
         <v>118</v>
       </c>
-      <c r="J35">
+      <c r="J35" s="3">
         <v>2011</v>
       </c>
       <c r="K35" t="s">
+        <v>13</v>
+      </c>
+      <c r="L35" t="s">
         <v>14</v>
       </c>
-      <c r="L35" t="s">
-        <v>15</v>
-      </c>
-      <c r="M35" t="s">
-        <v>16</v>
-      </c>
-      <c r="N35">
+      <c r="M35">
         <v>22</v>
       </c>
+      <c r="N35" t="s">
+        <v>8</v>
+      </c>
       <c r="O35" t="s">
-        <v>9</v>
-      </c>
-      <c r="P35" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>0</v>
       </c>
-      <c r="B36">
-        <v>0</v>
+      <c r="B36" t="s">
+        <v>40</v>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E36">
         <v>24.6</v>
@@ -2291,40 +2204,37 @@
       <c r="I36">
         <v>86</v>
       </c>
-      <c r="J36">
+      <c r="J36" s="3">
         <v>2011</v>
       </c>
       <c r="K36" t="s">
+        <v>13</v>
+      </c>
+      <c r="L36" t="s">
         <v>14</v>
       </c>
-      <c r="L36" t="s">
-        <v>15</v>
-      </c>
-      <c r="M36" t="s">
-        <v>16</v>
-      </c>
-      <c r="N36">
+      <c r="M36">
         <v>23</v>
       </c>
+      <c r="N36" t="s">
+        <v>8</v>
+      </c>
       <c r="O36" t="s">
-        <v>9</v>
-      </c>
-      <c r="P36" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>0</v>
       </c>
-      <c r="B37">
-        <v>0</v>
+      <c r="B37" t="s">
+        <v>40</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37">
         <v>24.6</v>
@@ -2341,40 +2251,37 @@
       <c r="I37">
         <v>76</v>
       </c>
-      <c r="J37">
+      <c r="J37" s="3">
         <v>2011</v>
       </c>
       <c r="K37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L37" t="s">
         <v>3</v>
       </c>
-      <c r="M37" t="s">
-        <v>4</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" t="s">
+        <v>10</v>
       </c>
       <c r="O37" t="s">
-        <v>11</v>
-      </c>
-      <c r="P37" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>0</v>
       </c>
-      <c r="B38">
-        <v>0</v>
+      <c r="B38" t="s">
+        <v>40</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E38">
         <v>23.78</v>
@@ -2391,40 +2298,37 @@
       <c r="I38">
         <v>51</v>
       </c>
-      <c r="J38">
+      <c r="J38" s="3">
         <v>2011</v>
       </c>
       <c r="K38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L38" t="s">
         <v>3</v>
       </c>
-      <c r="M38" t="s">
-        <v>4</v>
-      </c>
-      <c r="N38">
-        <v>1</v>
+      <c r="M38">
+        <v>1</v>
+      </c>
+      <c r="N38" t="s">
+        <v>10</v>
       </c>
       <c r="O38" t="s">
-        <v>11</v>
-      </c>
-      <c r="P38" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>0</v>
       </c>
-      <c r="B39">
-        <v>0</v>
+      <c r="B39" t="s">
+        <v>40</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E39">
         <v>22.96</v>
@@ -2441,40 +2345,37 @@
       <c r="I39">
         <v>25</v>
       </c>
-      <c r="J39">
+      <c r="J39" s="3">
         <v>2011</v>
       </c>
       <c r="K39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L39" t="s">
         <v>3</v>
       </c>
-      <c r="M39" t="s">
-        <v>4</v>
-      </c>
-      <c r="N39">
+      <c r="M39">
         <v>2</v>
       </c>
+      <c r="N39" t="s">
+        <v>10</v>
+      </c>
       <c r="O39" t="s">
-        <v>11</v>
-      </c>
-      <c r="P39" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>0</v>
       </c>
-      <c r="B40">
-        <v>0</v>
+      <c r="B40" t="s">
+        <v>40</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E40">
         <v>22.14</v>
@@ -2491,40 +2392,37 @@
       <c r="I40">
         <v>8</v>
       </c>
-      <c r="J40">
+      <c r="J40" s="3">
         <v>2011</v>
       </c>
       <c r="K40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L40" t="s">
         <v>3</v>
       </c>
-      <c r="M40" t="s">
-        <v>4</v>
-      </c>
-      <c r="N40">
+      <c r="M40">
         <v>3</v>
       </c>
+      <c r="N40" t="s">
+        <v>10</v>
+      </c>
       <c r="O40" t="s">
-        <v>11</v>
-      </c>
-      <c r="P40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>0</v>
       </c>
-      <c r="B41">
-        <v>0</v>
+      <c r="B41" t="s">
+        <v>40</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E41">
         <v>21.32</v>
@@ -2541,40 +2439,37 @@
       <c r="I41">
         <v>3</v>
       </c>
-      <c r="J41">
+      <c r="J41" s="3">
         <v>2011</v>
       </c>
       <c r="K41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L41" t="s">
         <v>3</v>
       </c>
-      <c r="M41" t="s">
+      <c r="M41">
         <v>4</v>
       </c>
-      <c r="N41">
-        <v>4</v>
+      <c r="N41" t="s">
+        <v>10</v>
       </c>
       <c r="O41" t="s">
-        <v>11</v>
-      </c>
-      <c r="P41" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>0</v>
       </c>
-      <c r="B42">
-        <v>0</v>
+      <c r="B42" t="s">
+        <v>40</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E42">
         <v>21.32</v>
@@ -2591,40 +2486,37 @@
       <c r="I42">
         <v>2</v>
       </c>
-      <c r="J42">
+      <c r="J42" s="3">
         <v>2011</v>
       </c>
       <c r="K42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L42" t="s">
         <v>3</v>
       </c>
-      <c r="M42" t="s">
-        <v>4</v>
-      </c>
-      <c r="N42">
+      <c r="M42">
         <v>5</v>
       </c>
+      <c r="N42" t="s">
+        <v>10</v>
+      </c>
       <c r="O42" t="s">
-        <v>11</v>
-      </c>
-      <c r="P42" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>0</v>
       </c>
-      <c r="B43">
-        <v>0</v>
+      <c r="B43" t="s">
+        <v>40</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E43">
         <v>18.04</v>
@@ -2641,40 +2533,37 @@
       <c r="I43">
         <v>10</v>
       </c>
-      <c r="J43">
+      <c r="J43" s="3">
         <v>2011</v>
       </c>
       <c r="K43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L43" t="s">
         <v>3</v>
       </c>
-      <c r="M43" t="s">
-        <v>4</v>
-      </c>
-      <c r="N43">
+      <c r="M43">
         <v>6</v>
       </c>
+      <c r="N43" t="s">
+        <v>11</v>
+      </c>
       <c r="O43" t="s">
-        <v>12</v>
-      </c>
-      <c r="P43" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>0</v>
       </c>
-      <c r="B44">
-        <v>0</v>
+      <c r="B44" t="s">
+        <v>40</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
       <c r="D44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E44">
         <v>16.399999999999999</v>
@@ -2691,40 +2580,37 @@
       <c r="I44">
         <v>13</v>
       </c>
-      <c r="J44">
+      <c r="J44" s="3">
         <v>2011</v>
       </c>
       <c r="K44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L44" t="s">
         <v>3</v>
       </c>
-      <c r="M44" t="s">
-        <v>4</v>
-      </c>
-      <c r="N44">
+      <c r="M44">
         <v>7</v>
       </c>
+      <c r="N44" t="s">
+        <v>11</v>
+      </c>
       <c r="O44" t="s">
-        <v>12</v>
-      </c>
-      <c r="P44" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>0</v>
       </c>
-      <c r="B45">
-        <v>0</v>
+      <c r="B45" t="s">
+        <v>40</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E45">
         <v>17.22</v>
@@ -2741,40 +2627,37 @@
       <c r="I45">
         <v>48</v>
       </c>
-      <c r="J45">
+      <c r="J45" s="3">
         <v>2011</v>
       </c>
       <c r="K45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L45" t="s">
         <v>3</v>
       </c>
-      <c r="M45" t="s">
-        <v>4</v>
-      </c>
-      <c r="N45">
+      <c r="M45">
         <v>8</v>
       </c>
+      <c r="N45" t="s">
+        <v>11</v>
+      </c>
       <c r="O45" t="s">
-        <v>12</v>
-      </c>
-      <c r="P45" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>0</v>
       </c>
-      <c r="B46">
-        <v>0</v>
+      <c r="B46" t="s">
+        <v>40</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E46">
         <v>17.22</v>
@@ -2791,40 +2674,37 @@
       <c r="I46">
         <v>76</v>
       </c>
-      <c r="J46">
+      <c r="J46" s="3">
         <v>2011</v>
       </c>
       <c r="K46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L46" t="s">
         <v>3</v>
       </c>
-      <c r="M46" t="s">
-        <v>4</v>
-      </c>
-      <c r="N46">
+      <c r="M46">
         <v>9</v>
       </c>
+      <c r="N46" t="s">
+        <v>11</v>
+      </c>
       <c r="O46" t="s">
-        <v>12</v>
-      </c>
-      <c r="P46" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>0</v>
       </c>
-      <c r="B47">
-        <v>0</v>
+      <c r="B47" t="s">
+        <v>40</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E47">
         <v>18.04</v>
@@ -2841,40 +2721,37 @@
       <c r="I47">
         <v>140</v>
       </c>
-      <c r="J47">
+      <c r="J47" s="3">
         <v>2011</v>
       </c>
       <c r="K47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L47" t="s">
         <v>3</v>
       </c>
-      <c r="M47" t="s">
-        <v>4</v>
-      </c>
-      <c r="N47">
+      <c r="M47">
         <v>10</v>
       </c>
+      <c r="N47" t="s">
+        <v>11</v>
+      </c>
       <c r="O47" t="s">
-        <v>12</v>
-      </c>
-      <c r="P47" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>0</v>
       </c>
-      <c r="B48">
-        <v>0</v>
+      <c r="B48" t="s">
+        <v>40</v>
       </c>
       <c r="C48">
         <v>0</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E48">
         <v>18.86</v>
@@ -2891,40 +2768,37 @@
       <c r="I48">
         <v>196</v>
       </c>
-      <c r="J48">
+      <c r="J48" s="3">
         <v>2011</v>
       </c>
       <c r="K48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L48" t="s">
         <v>3</v>
       </c>
-      <c r="M48" t="s">
-        <v>4</v>
-      </c>
-      <c r="N48">
+      <c r="M48">
         <v>11</v>
       </c>
+      <c r="N48" t="s">
+        <v>11</v>
+      </c>
       <c r="O48" t="s">
-        <v>12</v>
-      </c>
-      <c r="P48" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>0</v>
       </c>
-      <c r="B49">
-        <v>0</v>
+      <c r="B49" t="s">
+        <v>40</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E49">
         <v>18.86</v>
@@ -2941,40 +2815,37 @@
       <c r="I49">
         <v>267</v>
       </c>
-      <c r="J49">
+      <c r="J49" s="3">
         <v>2011</v>
       </c>
       <c r="K49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L49" t="s">
         <v>3</v>
       </c>
-      <c r="M49" t="s">
-        <v>4</v>
-      </c>
-      <c r="N49">
-        <v>12</v>
+      <c r="M49">
+        <v>12</v>
+      </c>
+      <c r="N49" t="s">
+        <v>15</v>
       </c>
       <c r="O49" t="s">
-        <v>17</v>
-      </c>
-      <c r="P49" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>0</v>
       </c>
-      <c r="B50">
-        <v>0</v>
+      <c r="B50" t="s">
+        <v>40</v>
       </c>
       <c r="C50">
         <v>0</v>
       </c>
       <c r="D50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E50">
         <v>20.5</v>
@@ -2991,40 +2862,37 @@
       <c r="I50">
         <v>301</v>
       </c>
-      <c r="J50">
+      <c r="J50" s="3">
         <v>2011</v>
       </c>
       <c r="K50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L50" t="s">
         <v>3</v>
       </c>
-      <c r="M50" t="s">
-        <v>4</v>
-      </c>
-      <c r="N50">
+      <c r="M50">
         <v>13</v>
       </c>
+      <c r="N50" t="s">
+        <v>15</v>
+      </c>
       <c r="O50" t="s">
-        <v>17</v>
-      </c>
-      <c r="P50" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>0</v>
       </c>
-      <c r="B51">
-        <v>0</v>
+      <c r="B51" t="s">
+        <v>40</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E51">
         <v>20.5</v>
@@ -3041,40 +2909,37 @@
       <c r="I51">
         <v>312</v>
       </c>
-      <c r="J51">
+      <c r="J51" s="3">
         <v>2011</v>
       </c>
       <c r="K51" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L51" t="s">
         <v>3</v>
       </c>
-      <c r="M51" t="s">
-        <v>4</v>
-      </c>
-      <c r="N51">
+      <c r="M51">
         <v>14</v>
       </c>
+      <c r="N51" t="s">
+        <v>18</v>
+      </c>
       <c r="O51" t="s">
-        <v>20</v>
-      </c>
-      <c r="P51" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>0</v>
       </c>
-      <c r="B52">
-        <v>0</v>
+      <c r="B52" t="s">
+        <v>40</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E52">
         <v>20.5</v>
@@ -3091,40 +2956,37 @@
       <c r="I52">
         <v>313</v>
       </c>
-      <c r="J52">
+      <c r="J52" s="3">
         <v>2011</v>
       </c>
       <c r="K52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L52" t="s">
         <v>3</v>
       </c>
-      <c r="M52" t="s">
-        <v>4</v>
-      </c>
-      <c r="N52">
+      <c r="M52">
         <v>15</v>
       </c>
+      <c r="N52" t="s">
+        <v>18</v>
+      </c>
       <c r="O52" t="s">
-        <v>20</v>
-      </c>
-      <c r="P52" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>0</v>
       </c>
-      <c r="B53">
-        <v>0</v>
+      <c r="B53" t="s">
+        <v>40</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E53">
         <v>20.5</v>
@@ -3141,40 +3003,37 @@
       <c r="I53">
         <v>304</v>
       </c>
-      <c r="J53">
+      <c r="J53" s="3">
         <v>2011</v>
       </c>
       <c r="K53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L53" t="s">
         <v>3</v>
       </c>
-      <c r="M53" t="s">
-        <v>4</v>
-      </c>
-      <c r="N53">
+      <c r="M53">
         <v>16</v>
       </c>
+      <c r="N53" t="s">
+        <v>18</v>
+      </c>
       <c r="O53" t="s">
-        <v>20</v>
-      </c>
-      <c r="P53" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>0</v>
       </c>
-      <c r="B54">
-        <v>0</v>
+      <c r="B54" t="s">
+        <v>40</v>
       </c>
       <c r="C54">
         <v>0</v>
       </c>
       <c r="D54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E54">
         <v>19.68</v>
@@ -3191,40 +3050,37 @@
       <c r="I54">
         <v>278</v>
       </c>
-      <c r="J54">
+      <c r="J54" s="3">
         <v>2011</v>
       </c>
       <c r="K54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L54" t="s">
         <v>3</v>
       </c>
-      <c r="M54" t="s">
-        <v>4</v>
-      </c>
-      <c r="N54">
+      <c r="M54">
         <v>17</v>
       </c>
+      <c r="N54" t="s">
+        <v>18</v>
+      </c>
       <c r="O54" t="s">
-        <v>20</v>
-      </c>
-      <c r="P54" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>0</v>
       </c>
-      <c r="B55">
-        <v>0</v>
+      <c r="B55" t="s">
+        <v>40</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E55">
         <v>18.86</v>
@@ -3241,40 +3097,37 @@
       <c r="I55">
         <v>217</v>
       </c>
-      <c r="J55">
+      <c r="J55" s="3">
         <v>2011</v>
       </c>
       <c r="K55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L55" t="s">
         <v>3</v>
       </c>
-      <c r="M55" t="s">
+      <c r="M55">
+        <v>18</v>
+      </c>
+      <c r="N55" t="s">
         <v>4</v>
-      </c>
-      <c r="N55">
-        <v>18</v>
       </c>
       <c r="O55" t="s">
         <v>5</v>
       </c>
-      <c r="P55" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>21</v>
-      </c>
-      <c r="B56">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="B56" t="s">
+        <v>40</v>
       </c>
       <c r="C56">
         <v>1</v>
       </c>
       <c r="D56" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E56">
         <v>26.24</v>
@@ -3291,40 +3144,37 @@
       <c r="I56">
         <v>6</v>
       </c>
-      <c r="J56">
+      <c r="J56" s="3">
         <v>2012</v>
       </c>
       <c r="K56" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L56" t="s">
-        <v>23</v>
-      </c>
-      <c r="M56" t="s">
+        <v>21</v>
+      </c>
+      <c r="M56">
+        <v>3</v>
+      </c>
+      <c r="N56" t="s">
+        <v>10</v>
+      </c>
+      <c r="O56" t="s">
         <v>16</v>
       </c>
-      <c r="N56">
-        <v>3</v>
-      </c>
-      <c r="O56" t="s">
-        <v>11</v>
-      </c>
-      <c r="P56" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>21</v>
-      </c>
-      <c r="B57">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="B57" t="s">
+        <v>40</v>
       </c>
       <c r="C57">
         <v>1</v>
       </c>
       <c r="D57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E57">
         <v>26.24</v>
@@ -3341,40 +3191,37 @@
       <c r="I57">
         <v>11</v>
       </c>
-      <c r="J57">
+      <c r="J57" s="3">
         <v>2012</v>
       </c>
       <c r="K57" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L57" t="s">
-        <v>23</v>
-      </c>
-      <c r="M57" t="s">
+        <v>21</v>
+      </c>
+      <c r="M57">
+        <v>4</v>
+      </c>
+      <c r="N57" t="s">
+        <v>10</v>
+      </c>
+      <c r="O57" t="s">
         <v>16</v>
       </c>
-      <c r="N57">
-        <v>4</v>
-      </c>
-      <c r="O57" t="s">
-        <v>11</v>
-      </c>
-      <c r="P57" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>21</v>
-      </c>
-      <c r="B58">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="B58" t="s">
+        <v>40</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
       <c r="D58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E58">
         <v>26.24</v>
@@ -3391,40 +3238,37 @@
       <c r="I58">
         <v>36</v>
       </c>
-      <c r="J58">
+      <c r="J58" s="3">
         <v>2012</v>
       </c>
       <c r="K58" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L58" t="s">
-        <v>23</v>
-      </c>
-      <c r="M58" t="s">
+        <v>21</v>
+      </c>
+      <c r="M58">
+        <v>5</v>
+      </c>
+      <c r="N58" t="s">
+        <v>10</v>
+      </c>
+      <c r="O58" t="s">
         <v>16</v>
       </c>
-      <c r="N58">
-        <v>5</v>
-      </c>
-      <c r="O58" t="s">
-        <v>11</v>
-      </c>
-      <c r="P58" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>21</v>
-      </c>
-      <c r="B59">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="B59" t="s">
+        <v>40</v>
       </c>
       <c r="C59">
         <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E59">
         <v>25.42</v>
@@ -3441,40 +3285,37 @@
       <c r="I59">
         <v>159</v>
       </c>
-      <c r="J59">
+      <c r="J59" s="3">
         <v>2012</v>
       </c>
       <c r="K59" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L59" t="s">
-        <v>23</v>
-      </c>
-      <c r="M59" t="s">
+        <v>21</v>
+      </c>
+      <c r="M59">
+        <v>6</v>
+      </c>
+      <c r="N59" t="s">
+        <v>11</v>
+      </c>
+      <c r="O59" t="s">
         <v>16</v>
       </c>
-      <c r="N59">
-        <v>6</v>
-      </c>
-      <c r="O59" t="s">
-        <v>12</v>
-      </c>
-      <c r="P59" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>21</v>
-      </c>
-      <c r="B60">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="B60" t="s">
+        <v>40</v>
       </c>
       <c r="C60">
         <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E60">
         <v>27.06</v>
@@ -3491,40 +3332,37 @@
       <c r="I60">
         <v>436</v>
       </c>
-      <c r="J60">
+      <c r="J60" s="3">
         <v>2012</v>
       </c>
       <c r="K60" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L60" t="s">
-        <v>23</v>
-      </c>
-      <c r="M60" t="s">
-        <v>16</v>
-      </c>
-      <c r="N60">
+        <v>21</v>
+      </c>
+      <c r="M60">
         <v>7</v>
       </c>
+      <c r="N60" t="s">
+        <v>11</v>
+      </c>
       <c r="O60" t="s">
-        <v>12</v>
-      </c>
-      <c r="P60" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>21</v>
-      </c>
-      <c r="B61">
-        <v>0</v>
+      <c r="B61" t="s">
+        <v>40</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E61">
         <v>30.34</v>
@@ -3541,40 +3379,37 @@
       <c r="I61">
         <v>305</v>
       </c>
-      <c r="J61">
+      <c r="J61" s="3">
         <v>2012</v>
       </c>
       <c r="K61" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L61" t="s">
-        <v>23</v>
-      </c>
-      <c r="M61" t="s">
-        <v>16</v>
-      </c>
-      <c r="N61">
+        <v>21</v>
+      </c>
+      <c r="M61">
         <v>9</v>
       </c>
+      <c r="N61" t="s">
+        <v>11</v>
+      </c>
       <c r="O61" t="s">
-        <v>12</v>
-      </c>
-      <c r="P61" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>21</v>
-      </c>
-      <c r="B62">
-        <v>0</v>
+      <c r="B62" t="s">
+        <v>40</v>
       </c>
       <c r="C62">
         <v>1</v>
       </c>
       <c r="D62" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E62">
         <v>31.16</v>
@@ -3591,40 +3426,37 @@
       <c r="I62">
         <v>199</v>
       </c>
-      <c r="J62">
+      <c r="J62" s="3">
         <v>2012</v>
       </c>
       <c r="K62" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L62" t="s">
-        <v>23</v>
-      </c>
-      <c r="M62" t="s">
-        <v>16</v>
-      </c>
-      <c r="N62">
+        <v>21</v>
+      </c>
+      <c r="M62">
         <v>10</v>
       </c>
+      <c r="N62" t="s">
+        <v>11</v>
+      </c>
       <c r="O62" t="s">
-        <v>12</v>
-      </c>
-      <c r="P62" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>21</v>
-      </c>
-      <c r="B63">
-        <v>0</v>
+      <c r="B63" t="s">
+        <v>40</v>
       </c>
       <c r="C63">
         <v>1</v>
       </c>
       <c r="D63" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E63">
         <v>31.16</v>
@@ -3641,40 +3473,37 @@
       <c r="I63">
         <v>245</v>
       </c>
-      <c r="J63">
+      <c r="J63" s="3">
         <v>2012</v>
       </c>
       <c r="K63" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L63" t="s">
-        <v>23</v>
-      </c>
-      <c r="M63" t="s">
-        <v>16</v>
-      </c>
-      <c r="N63">
+        <v>21</v>
+      </c>
+      <c r="M63">
         <v>11</v>
       </c>
+      <c r="N63" t="s">
+        <v>11</v>
+      </c>
       <c r="O63" t="s">
-        <v>12</v>
-      </c>
-      <c r="P63" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>21</v>
-      </c>
-      <c r="B64">
-        <v>0</v>
+      <c r="B64" t="s">
+        <v>40</v>
       </c>
       <c r="C64">
         <v>1</v>
       </c>
       <c r="D64" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E64">
         <v>31.98</v>
@@ -3691,40 +3520,37 @@
       <c r="I64">
         <v>276</v>
       </c>
-      <c r="J64">
+      <c r="J64" s="3">
         <v>2012</v>
       </c>
       <c r="K64" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L64" t="s">
-        <v>23</v>
-      </c>
-      <c r="M64" t="s">
-        <v>16</v>
-      </c>
-      <c r="N64">
-        <v>12</v>
+        <v>21</v>
+      </c>
+      <c r="M64">
+        <v>12</v>
+      </c>
+      <c r="N64" t="s">
+        <v>15</v>
       </c>
       <c r="O64" t="s">
         <v>17</v>
       </c>
-      <c r="P64" t="s">
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>21</v>
-      </c>
-      <c r="B65">
-        <v>0</v>
+      <c r="B65" t="s">
+        <v>40</v>
       </c>
       <c r="C65">
         <v>1</v>
       </c>
       <c r="D65" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E65">
         <v>31.98</v>
@@ -3741,40 +3567,37 @@
       <c r="I65">
         <v>254</v>
       </c>
-      <c r="J65">
+      <c r="J65" s="3">
         <v>2012</v>
       </c>
       <c r="K65" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L65" t="s">
-        <v>23</v>
-      </c>
-      <c r="M65" t="s">
-        <v>16</v>
-      </c>
-      <c r="N65">
+        <v>21</v>
+      </c>
+      <c r="M65">
         <v>13</v>
+      </c>
+      <c r="N65" t="s">
+        <v>15</v>
       </c>
       <c r="O65" t="s">
         <v>17</v>
       </c>
-      <c r="P65" t="s">
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>21</v>
-      </c>
-      <c r="B66">
-        <v>0</v>
+      <c r="B66" t="s">
+        <v>40</v>
       </c>
       <c r="C66">
         <v>1</v>
       </c>
       <c r="D66" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E66">
         <v>32.799999999999997</v>
@@ -3791,40 +3614,37 @@
       <c r="I66">
         <v>248</v>
       </c>
-      <c r="J66">
+      <c r="J66" s="3">
         <v>2012</v>
       </c>
       <c r="K66" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L66" t="s">
-        <v>23</v>
-      </c>
-      <c r="M66" t="s">
-        <v>16</v>
-      </c>
-      <c r="N66">
+        <v>21</v>
+      </c>
+      <c r="M66">
         <v>14</v>
       </c>
+      <c r="N66" t="s">
+        <v>18</v>
+      </c>
       <c r="O66" t="s">
-        <v>20</v>
-      </c>
-      <c r="P66" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>21</v>
-      </c>
-      <c r="B67">
-        <v>0</v>
+      <c r="B67" t="s">
+        <v>40</v>
       </c>
       <c r="C67">
         <v>1</v>
       </c>
       <c r="D67" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E67">
         <v>33.619999999999997</v>
@@ -3841,40 +3661,37 @@
       <c r="I67">
         <v>274</v>
       </c>
-      <c r="J67">
+      <c r="J67" s="3">
         <v>2012</v>
       </c>
       <c r="K67" t="s">
+        <v>20</v>
+      </c>
+      <c r="L67" t="s">
+        <v>21</v>
+      </c>
+      <c r="M67">
+        <v>15</v>
+      </c>
+      <c r="N67" t="s">
+        <v>18</v>
+      </c>
+      <c r="O67" t="s">
         <v>22</v>
       </c>
-      <c r="L67" t="s">
-        <v>23</v>
-      </c>
-      <c r="M67" t="s">
-        <v>16</v>
-      </c>
-      <c r="N67">
-        <v>15</v>
-      </c>
-      <c r="O67" t="s">
-        <v>20</v>
-      </c>
-      <c r="P67" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>21</v>
-      </c>
-      <c r="B68">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="B68" t="s">
+        <v>40</v>
       </c>
       <c r="C68">
         <v>1</v>
       </c>
       <c r="D68" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E68">
         <v>32.799999999999997</v>
@@ -3891,40 +3708,37 @@
       <c r="I68">
         <v>464</v>
       </c>
-      <c r="J68">
+      <c r="J68" s="3">
         <v>2012</v>
       </c>
       <c r="K68" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L68" t="s">
-        <v>23</v>
-      </c>
-      <c r="M68" t="s">
+        <v>21</v>
+      </c>
+      <c r="M68">
         <v>16</v>
       </c>
-      <c r="N68">
-        <v>16</v>
+      <c r="N68" t="s">
+        <v>18</v>
       </c>
       <c r="O68" t="s">
-        <v>20</v>
-      </c>
-      <c r="P68" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>21</v>
-      </c>
-      <c r="B69">
-        <v>0</v>
+      <c r="B69" t="s">
+        <v>40</v>
       </c>
       <c r="C69">
         <v>1</v>
       </c>
       <c r="D69" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E69">
         <v>30.34</v>
@@ -3941,40 +3755,37 @@
       <c r="I69">
         <v>555</v>
       </c>
-      <c r="J69">
+      <c r="J69" s="3">
         <v>2012</v>
       </c>
       <c r="K69" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L69" t="s">
-        <v>23</v>
-      </c>
-      <c r="M69" t="s">
-        <v>16</v>
-      </c>
-      <c r="N69">
+        <v>21</v>
+      </c>
+      <c r="M69">
         <v>19</v>
       </c>
+      <c r="N69" t="s">
+        <v>4</v>
+      </c>
       <c r="O69" t="s">
-        <v>5</v>
-      </c>
-      <c r="P69" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>21</v>
-      </c>
-      <c r="B70">
-        <v>0</v>
+      <c r="B70" t="s">
+        <v>40</v>
       </c>
       <c r="C70">
         <v>1</v>
       </c>
       <c r="D70" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E70">
         <v>30.34</v>
@@ -3991,40 +3802,37 @@
       <c r="I70">
         <v>432</v>
       </c>
-      <c r="J70">
+      <c r="J70" s="3">
         <v>2012</v>
       </c>
       <c r="K70" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L70" t="s">
-        <v>23</v>
-      </c>
-      <c r="M70" t="s">
-        <v>16</v>
-      </c>
-      <c r="N70">
+        <v>21</v>
+      </c>
+      <c r="M70">
         <v>20</v>
       </c>
+      <c r="N70" t="s">
+        <v>4</v>
+      </c>
       <c r="O70" t="s">
-        <v>5</v>
-      </c>
-      <c r="P70" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>21</v>
-      </c>
-      <c r="B71">
-        <v>0</v>
+      <c r="B71" t="s">
+        <v>40</v>
       </c>
       <c r="C71">
         <v>1</v>
       </c>
       <c r="D71" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E71">
         <v>29.52</v>
@@ -4041,40 +3849,37 @@
       <c r="I71">
         <v>290</v>
       </c>
-      <c r="J71">
+      <c r="J71" s="3">
         <v>2012</v>
       </c>
       <c r="K71" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L71" t="s">
-        <v>23</v>
-      </c>
-      <c r="M71" t="s">
-        <v>16</v>
-      </c>
-      <c r="N71">
         <v>21</v>
       </c>
+      <c r="M71">
+        <v>21</v>
+      </c>
+      <c r="N71" t="s">
+        <v>8</v>
+      </c>
       <c r="O71" t="s">
-        <v>9</v>
-      </c>
-      <c r="P71" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>21</v>
-      </c>
-      <c r="B72">
-        <v>0</v>
+      <c r="B72" t="s">
+        <v>40</v>
       </c>
       <c r="C72">
         <v>1</v>
       </c>
       <c r="D72" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E72">
         <v>29.52</v>
@@ -4091,40 +3896,37 @@
       <c r="I72">
         <v>192</v>
       </c>
-      <c r="J72">
+      <c r="J72" s="3">
         <v>2012</v>
       </c>
       <c r="K72" t="s">
+        <v>20</v>
+      </c>
+      <c r="L72" t="s">
+        <v>21</v>
+      </c>
+      <c r="M72">
         <v>22</v>
       </c>
-      <c r="L72" t="s">
-        <v>23</v>
-      </c>
-      <c r="M72" t="s">
-        <v>16</v>
-      </c>
-      <c r="N72">
-        <v>22</v>
+      <c r="N72" t="s">
+        <v>8</v>
       </c>
       <c r="O72" t="s">
-        <v>9</v>
-      </c>
-      <c r="P72" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>21</v>
-      </c>
-      <c r="B73">
-        <v>0</v>
+      <c r="B73" t="s">
+        <v>40</v>
       </c>
       <c r="C73">
         <v>1</v>
       </c>
       <c r="D73" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E73">
         <v>28.7</v>
@@ -4141,40 +3943,37 @@
       <c r="I73">
         <v>128</v>
       </c>
-      <c r="J73">
+      <c r="J73" s="3">
         <v>2012</v>
       </c>
       <c r="K73" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L73" t="s">
+        <v>21</v>
+      </c>
+      <c r="M73">
         <v>23</v>
       </c>
-      <c r="M73" t="s">
-        <v>16</v>
-      </c>
-      <c r="N73">
-        <v>23</v>
+      <c r="N73" t="s">
+        <v>8</v>
       </c>
       <c r="O73" t="s">
-        <v>9</v>
-      </c>
-      <c r="P73" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>21</v>
-      </c>
-      <c r="B74">
-        <v>0</v>
+      <c r="B74" t="s">
+        <v>40</v>
       </c>
       <c r="C74">
         <v>1</v>
       </c>
       <c r="D74" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E74">
         <v>28.7</v>
@@ -4191,40 +3990,37 @@
       <c r="I74">
         <v>60</v>
       </c>
-      <c r="J74">
+      <c r="J74" s="3">
         <v>2012</v>
       </c>
       <c r="K74" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L74" t="s">
-        <v>25</v>
-      </c>
-      <c r="M74" t="s">
-        <v>16</v>
-      </c>
-      <c r="N74">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74" t="s">
+        <v>10</v>
       </c>
       <c r="O74" t="s">
-        <v>11</v>
-      </c>
-      <c r="P74" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>21</v>
-      </c>
-      <c r="B75">
-        <v>0</v>
+      <c r="B75" t="s">
+        <v>40</v>
       </c>
       <c r="C75">
         <v>1</v>
       </c>
       <c r="D75" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E75">
         <v>27.88</v>
@@ -4241,40 +4037,37 @@
       <c r="I75">
         <v>27</v>
       </c>
-      <c r="J75">
+      <c r="J75" s="3">
         <v>2012</v>
       </c>
       <c r="K75" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L75" t="s">
-        <v>25</v>
-      </c>
-      <c r="M75" t="s">
-        <v>16</v>
-      </c>
-      <c r="N75">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="M75">
+        <v>1</v>
+      </c>
+      <c r="N75" t="s">
+        <v>10</v>
       </c>
       <c r="O75" t="s">
-        <v>11</v>
-      </c>
-      <c r="P75" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>21</v>
-      </c>
-      <c r="B76">
-        <v>0</v>
+      <c r="B76" t="s">
+        <v>40</v>
       </c>
       <c r="C76">
         <v>1</v>
       </c>
       <c r="D76" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E76">
         <v>27.88</v>
@@ -4291,40 +4084,37 @@
       <c r="I76">
         <v>11</v>
       </c>
-      <c r="J76">
+      <c r="J76" s="3">
         <v>2012</v>
       </c>
       <c r="K76" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L76" t="s">
-        <v>25</v>
-      </c>
-      <c r="M76" t="s">
-        <v>16</v>
-      </c>
-      <c r="N76">
+        <v>23</v>
+      </c>
+      <c r="M76">
         <v>2</v>
       </c>
+      <c r="N76" t="s">
+        <v>10</v>
+      </c>
       <c r="O76" t="s">
-        <v>11</v>
-      </c>
-      <c r="P76" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>21</v>
-      </c>
-      <c r="B77">
-        <v>0</v>
+      <c r="B77" t="s">
+        <v>40</v>
       </c>
       <c r="C77">
         <v>1</v>
       </c>
       <c r="D77" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E77">
         <v>27.88</v>
@@ -4341,40 +4131,37 @@
       <c r="I77">
         <v>3</v>
       </c>
-      <c r="J77">
+      <c r="J77" s="3">
         <v>2012</v>
       </c>
       <c r="K77" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L77" t="s">
-        <v>25</v>
-      </c>
-      <c r="M77" t="s">
-        <v>16</v>
-      </c>
-      <c r="N77">
+        <v>23</v>
+      </c>
+      <c r="M77">
         <v>3</v>
       </c>
+      <c r="N77" t="s">
+        <v>10</v>
+      </c>
       <c r="O77" t="s">
-        <v>11</v>
-      </c>
-      <c r="P77" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>21</v>
-      </c>
-      <c r="B78">
-        <v>0</v>
+      <c r="B78" t="s">
+        <v>40</v>
       </c>
       <c r="C78">
         <v>1</v>
       </c>
       <c r="D78" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E78">
         <v>27.88</v>
@@ -4391,40 +4178,37 @@
       <c r="I78">
         <v>5</v>
       </c>
-      <c r="J78">
+      <c r="J78" s="3">
         <v>2012</v>
       </c>
       <c r="K78" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L78" t="s">
-        <v>25</v>
-      </c>
-      <c r="M78" t="s">
-        <v>16</v>
-      </c>
-      <c r="N78">
+        <v>23</v>
+      </c>
+      <c r="M78">
         <v>4</v>
       </c>
+      <c r="N78" t="s">
+        <v>10</v>
+      </c>
       <c r="O78" t="s">
-        <v>11</v>
-      </c>
-      <c r="P78" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>21</v>
-      </c>
-      <c r="B79">
-        <v>0</v>
+      <c r="B79" t="s">
+        <v>40</v>
       </c>
       <c r="C79">
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E79">
         <v>27.88</v>
@@ -4441,34 +4225,31 @@
       <c r="I79">
         <v>36</v>
       </c>
-      <c r="J79">
+      <c r="J79" s="3">
         <v>2012</v>
       </c>
       <c r="K79" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L79" t="s">
-        <v>25</v>
-      </c>
-      <c r="M79" t="s">
-        <v>16</v>
-      </c>
-      <c r="N79">
+        <v>23</v>
+      </c>
+      <c r="M79">
         <v>5</v>
       </c>
+      <c r="N79" t="s">
+        <v>10</v>
+      </c>
       <c r="O79" t="s">
-        <v>11</v>
-      </c>
-      <c r="P79" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>21</v>
-      </c>
-      <c r="B80">
-        <v>0</v>
+      <c r="B80" t="s">
+        <v>40</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -4491,40 +4272,37 @@
       <c r="I80">
         <v>64</v>
       </c>
-      <c r="J80">
+      <c r="J80" s="3">
         <v>2012</v>
       </c>
       <c r="K80" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L80" t="s">
-        <v>25</v>
-      </c>
-      <c r="M80" t="s">
+        <v>23</v>
+      </c>
+      <c r="M80">
+        <v>6</v>
+      </c>
+      <c r="N80" t="s">
+        <v>11</v>
+      </c>
+      <c r="O80" t="s">
         <v>16</v>
       </c>
-      <c r="N80">
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>19</v>
+      </c>
+      <c r="B81" t="s">
+        <v>40</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="D81" t="s">
         <v>6</v>
-      </c>
-      <c r="O80" t="s">
-        <v>12</v>
-      </c>
-      <c r="P80" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>21</v>
-      </c>
-      <c r="B81">
-        <v>0</v>
-      </c>
-      <c r="C81">
-        <v>1</v>
-      </c>
-      <c r="D81" t="s">
-        <v>7</v>
       </c>
       <c r="E81">
         <v>27.06</v>
@@ -4541,40 +4319,37 @@
       <c r="I81">
         <v>179</v>
       </c>
-      <c r="J81">
+      <c r="J81" s="3">
         <v>2012</v>
       </c>
       <c r="K81" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L81" t="s">
-        <v>25</v>
-      </c>
-      <c r="M81" t="s">
+        <v>23</v>
+      </c>
+      <c r="M81">
+        <v>7</v>
+      </c>
+      <c r="N81" t="s">
+        <v>11</v>
+      </c>
+      <c r="O81" t="s">
         <v>16</v>
       </c>
-      <c r="N81">
-        <v>7</v>
-      </c>
-      <c r="O81" t="s">
-        <v>12</v>
-      </c>
-      <c r="P81" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>21</v>
-      </c>
-      <c r="B82">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="B82" t="s">
+        <v>40</v>
       </c>
       <c r="C82">
         <v>1</v>
       </c>
       <c r="D82" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E82">
         <v>27.06</v>
@@ -4591,40 +4366,37 @@
       <c r="I82">
         <v>618</v>
       </c>
-      <c r="J82">
+      <c r="J82" s="3">
         <v>2012</v>
       </c>
       <c r="K82" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L82" t="s">
-        <v>25</v>
-      </c>
-      <c r="M82" t="s">
+        <v>23</v>
+      </c>
+      <c r="M82">
+        <v>8</v>
+      </c>
+      <c r="N82" t="s">
+        <v>11</v>
+      </c>
+      <c r="O82" t="s">
         <v>16</v>
       </c>
-      <c r="N82">
-        <v>8</v>
-      </c>
-      <c r="O82" t="s">
-        <v>12</v>
-      </c>
-      <c r="P82" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>21</v>
-      </c>
-      <c r="B83">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="B83" t="s">
+        <v>40</v>
       </c>
       <c r="C83">
         <v>1</v>
       </c>
       <c r="D83" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E83">
         <v>28.7</v>
@@ -4641,40 +4413,37 @@
       <c r="I83">
         <v>402</v>
       </c>
-      <c r="J83">
+      <c r="J83" s="3">
         <v>2012</v>
       </c>
       <c r="K83" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L83" t="s">
-        <v>25</v>
-      </c>
-      <c r="M83" t="s">
-        <v>16</v>
-      </c>
-      <c r="N83">
+        <v>23</v>
+      </c>
+      <c r="M83">
         <v>9</v>
       </c>
+      <c r="N83" t="s">
+        <v>11</v>
+      </c>
       <c r="O83" t="s">
-        <v>12</v>
-      </c>
-      <c r="P83" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>21</v>
-      </c>
-      <c r="B84">
-        <v>0</v>
+      <c r="B84" t="s">
+        <v>40</v>
       </c>
       <c r="C84">
         <v>1</v>
       </c>
       <c r="D84" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E84">
         <v>28.7</v>
@@ -4691,40 +4460,37 @@
       <c r="I84">
         <v>208</v>
       </c>
-      <c r="J84">
+      <c r="J84" s="3">
         <v>2012</v>
       </c>
       <c r="K84" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L84" t="s">
-        <v>25</v>
-      </c>
-      <c r="M84" t="s">
-        <v>16</v>
-      </c>
-      <c r="N84">
+        <v>23</v>
+      </c>
+      <c r="M84">
         <v>10</v>
       </c>
+      <c r="N84" t="s">
+        <v>11</v>
+      </c>
       <c r="O84" t="s">
-        <v>12</v>
-      </c>
-      <c r="P84" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>21</v>
-      </c>
-      <c r="B85">
-        <v>0</v>
+      <c r="B85" t="s">
+        <v>40</v>
       </c>
       <c r="C85">
         <v>1</v>
       </c>
       <c r="D85" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E85">
         <v>30.34</v>
@@ -4741,40 +4507,37 @@
       <c r="I85">
         <v>196</v>
       </c>
-      <c r="J85">
+      <c r="J85" s="3">
         <v>2012</v>
       </c>
       <c r="K85" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L85" t="s">
-        <v>25</v>
-      </c>
-      <c r="M85" t="s">
-        <v>16</v>
-      </c>
-      <c r="N85">
+        <v>23</v>
+      </c>
+      <c r="M85">
         <v>11</v>
       </c>
+      <c r="N85" t="s">
+        <v>11</v>
+      </c>
       <c r="O85" t="s">
-        <v>12</v>
-      </c>
-      <c r="P85" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>21</v>
-      </c>
-      <c r="B86">
-        <v>0</v>
+      <c r="B86" t="s">
+        <v>40</v>
       </c>
       <c r="C86">
         <v>1</v>
       </c>
       <c r="D86" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E86">
         <v>31.98</v>
@@ -4791,40 +4554,37 @@
       <c r="I86">
         <v>300</v>
       </c>
-      <c r="J86">
+      <c r="J86" s="3">
         <v>2012</v>
       </c>
       <c r="K86" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L86" t="s">
-        <v>25</v>
-      </c>
-      <c r="M86" t="s">
-        <v>16</v>
-      </c>
-      <c r="N86">
-        <v>12</v>
+        <v>23</v>
+      </c>
+      <c r="M86">
+        <v>12</v>
+      </c>
+      <c r="N86" t="s">
+        <v>15</v>
       </c>
       <c r="O86" t="s">
         <v>17</v>
       </c>
-      <c r="P86" t="s">
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
-        <v>21</v>
-      </c>
-      <c r="B87">
-        <v>0</v>
+      <c r="B87" t="s">
+        <v>40</v>
       </c>
       <c r="C87">
         <v>1</v>
       </c>
       <c r="D87" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E87">
         <v>32.799999999999997</v>
@@ -4841,40 +4601,37 @@
       <c r="I87">
         <v>286</v>
       </c>
-      <c r="J87">
+      <c r="J87" s="3">
         <v>2012</v>
       </c>
       <c r="K87" t="s">
+        <v>20</v>
+      </c>
+      <c r="L87" t="s">
+        <v>23</v>
+      </c>
+      <c r="M87">
+        <v>13</v>
+      </c>
+      <c r="N87" t="s">
+        <v>15</v>
+      </c>
+      <c r="O87" t="s">
         <v>22</v>
       </c>
-      <c r="L87" t="s">
-        <v>25</v>
-      </c>
-      <c r="M87" t="s">
-        <v>16</v>
-      </c>
-      <c r="N87">
-        <v>13</v>
-      </c>
-      <c r="O87" t="s">
-        <v>17</v>
-      </c>
-      <c r="P87" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>21</v>
-      </c>
-      <c r="B88">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="B88" t="s">
+        <v>40</v>
       </c>
       <c r="C88">
         <v>1</v>
       </c>
       <c r="D88" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E88">
         <v>33.619999999999997</v>
@@ -4891,40 +4648,37 @@
       <c r="I88">
         <v>255</v>
       </c>
-      <c r="J88">
+      <c r="J88" s="3">
         <v>2012</v>
       </c>
       <c r="K88" t="s">
+        <v>20</v>
+      </c>
+      <c r="L88" t="s">
+        <v>23</v>
+      </c>
+      <c r="M88">
+        <v>14</v>
+      </c>
+      <c r="N88" t="s">
+        <v>18</v>
+      </c>
+      <c r="O88" t="s">
         <v>22</v>
       </c>
-      <c r="L88" t="s">
-        <v>25</v>
-      </c>
-      <c r="M88" t="s">
-        <v>16</v>
-      </c>
-      <c r="N88">
-        <v>14</v>
-      </c>
-      <c r="O88" t="s">
-        <v>20</v>
-      </c>
-      <c r="P88" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>21</v>
-      </c>
-      <c r="B89">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="B89" t="s">
+        <v>40</v>
       </c>
       <c r="C89">
         <v>1</v>
       </c>
       <c r="D89" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E89">
         <v>33.619999999999997</v>
@@ -4941,40 +4695,37 @@
       <c r="I89">
         <v>283</v>
       </c>
-      <c r="J89">
+      <c r="J89" s="3">
         <v>2012</v>
       </c>
       <c r="K89" t="s">
+        <v>20</v>
+      </c>
+      <c r="L89" t="s">
+        <v>23</v>
+      </c>
+      <c r="M89">
+        <v>15</v>
+      </c>
+      <c r="N89" t="s">
+        <v>18</v>
+      </c>
+      <c r="O89" t="s">
         <v>22</v>
       </c>
-      <c r="L89" t="s">
-        <v>25</v>
-      </c>
-      <c r="M89" t="s">
-        <v>16</v>
-      </c>
-      <c r="N89">
-        <v>15</v>
-      </c>
-      <c r="O89" t="s">
-        <v>20</v>
-      </c>
-      <c r="P89" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>21</v>
-      </c>
-      <c r="B90">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="B90" t="s">
+        <v>40</v>
       </c>
       <c r="C90">
         <v>1</v>
       </c>
       <c r="D90" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E90">
         <v>33.619999999999997</v>
@@ -4991,40 +4742,37 @@
       <c r="I90">
         <v>458</v>
       </c>
-      <c r="J90">
+      <c r="J90" s="3">
         <v>2012</v>
       </c>
       <c r="K90" t="s">
+        <v>20</v>
+      </c>
+      <c r="L90" t="s">
+        <v>23</v>
+      </c>
+      <c r="M90">
+        <v>16</v>
+      </c>
+      <c r="N90" t="s">
+        <v>18</v>
+      </c>
+      <c r="O90" t="s">
         <v>22</v>
       </c>
-      <c r="L90" t="s">
-        <v>25</v>
-      </c>
-      <c r="M90" t="s">
-        <v>16</v>
-      </c>
-      <c r="N90">
-        <v>16</v>
-      </c>
-      <c r="O90" t="s">
-        <v>20</v>
-      </c>
-      <c r="P90" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>21</v>
-      </c>
-      <c r="B91">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="B91" t="s">
+        <v>40</v>
       </c>
       <c r="C91">
         <v>1</v>
       </c>
       <c r="D91" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E91">
         <v>31.16</v>
@@ -5041,40 +4789,37 @@
       <c r="I91">
         <v>627</v>
       </c>
-      <c r="J91">
+      <c r="J91" s="3">
         <v>2012</v>
       </c>
       <c r="K91" t="s">
+        <v>20</v>
+      </c>
+      <c r="L91" t="s">
+        <v>23</v>
+      </c>
+      <c r="M91">
+        <v>19</v>
+      </c>
+      <c r="N91" t="s">
+        <v>4</v>
+      </c>
+      <c r="O91" t="s">
         <v>22</v>
       </c>
-      <c r="L91" t="s">
-        <v>25</v>
-      </c>
-      <c r="M91" t="s">
-        <v>16</v>
-      </c>
-      <c r="N91">
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
         <v>19</v>
       </c>
-      <c r="O91" t="s">
-        <v>5</v>
-      </c>
-      <c r="P91" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>21</v>
-      </c>
-      <c r="B92">
-        <v>0</v>
+      <c r="B92" t="s">
+        <v>40</v>
       </c>
       <c r="C92">
         <v>1</v>
       </c>
       <c r="D92" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E92">
         <v>30.34</v>
@@ -5091,40 +4836,37 @@
       <c r="I92">
         <v>436</v>
       </c>
-      <c r="J92">
+      <c r="J92" s="3">
         <v>2012</v>
       </c>
       <c r="K92" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L92" t="s">
-        <v>25</v>
-      </c>
-      <c r="M92" t="s">
-        <v>16</v>
-      </c>
-      <c r="N92">
+        <v>23</v>
+      </c>
+      <c r="M92">
         <v>20</v>
       </c>
+      <c r="N92" t="s">
+        <v>4</v>
+      </c>
       <c r="O92" t="s">
-        <v>5</v>
-      </c>
-      <c r="P92" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
-        <v>21</v>
-      </c>
-      <c r="B93">
-        <v>0</v>
+      <c r="B93" t="s">
+        <v>40</v>
       </c>
       <c r="C93">
         <v>1</v>
       </c>
       <c r="D93" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E93">
         <v>30.34</v>
@@ -5141,40 +4883,37 @@
       <c r="I93">
         <v>308</v>
       </c>
-      <c r="J93">
+      <c r="J93" s="3">
         <v>2012</v>
       </c>
       <c r="K93" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L93" t="s">
-        <v>25</v>
-      </c>
-      <c r="M93" t="s">
-        <v>16</v>
-      </c>
-      <c r="N93">
+        <v>23</v>
+      </c>
+      <c r="M93">
         <v>21</v>
       </c>
+      <c r="N93" t="s">
+        <v>8</v>
+      </c>
       <c r="O93" t="s">
-        <v>9</v>
-      </c>
-      <c r="P93" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>21</v>
-      </c>
-      <c r="B94">
-        <v>0</v>
+      <c r="B94" t="s">
+        <v>40</v>
       </c>
       <c r="C94">
         <v>1</v>
       </c>
       <c r="D94" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E94">
         <v>29.52</v>
@@ -5191,40 +4930,37 @@
       <c r="I94">
         <v>189</v>
       </c>
-      <c r="J94">
+      <c r="J94" s="3">
         <v>2012</v>
       </c>
       <c r="K94" t="s">
+        <v>20</v>
+      </c>
+      <c r="L94" t="s">
+        <v>23</v>
+      </c>
+      <c r="M94">
         <v>22</v>
       </c>
-      <c r="L94" t="s">
-        <v>25</v>
-      </c>
-      <c r="M94" t="s">
-        <v>16</v>
-      </c>
-      <c r="N94">
-        <v>22</v>
+      <c r="N94" t="s">
+        <v>8</v>
       </c>
       <c r="O94" t="s">
-        <v>9</v>
-      </c>
-      <c r="P94" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
-        <v>21</v>
-      </c>
-      <c r="B95">
-        <v>0</v>
+      <c r="B95" t="s">
+        <v>40</v>
       </c>
       <c r="C95">
         <v>1</v>
       </c>
       <c r="D95" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E95">
         <v>29.52</v>
@@ -5241,40 +4977,37 @@
       <c r="I95">
         <v>167</v>
       </c>
-      <c r="J95">
+      <c r="J95" s="3">
         <v>2012</v>
       </c>
       <c r="K95" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L95" t="s">
-        <v>25</v>
-      </c>
-      <c r="M95" t="s">
-        <v>16</v>
-      </c>
-      <c r="N95">
         <v>23</v>
       </c>
+      <c r="M95">
+        <v>23</v>
+      </c>
+      <c r="N95" t="s">
+        <v>8</v>
+      </c>
       <c r="O95" t="s">
-        <v>9</v>
-      </c>
-      <c r="P95" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>21</v>
-      </c>
-      <c r="B96">
-        <v>0</v>
+      <c r="B96" t="s">
+        <v>40</v>
       </c>
       <c r="C96">
         <v>1</v>
       </c>
       <c r="D96" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E96">
         <v>28.7</v>
@@ -5291,40 +5024,37 @@
       <c r="I96">
         <v>60</v>
       </c>
-      <c r="J96">
+      <c r="J96" s="3">
         <v>2012</v>
       </c>
       <c r="K96" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L96" t="s">
-        <v>26</v>
-      </c>
-      <c r="M96" t="s">
-        <v>16</v>
-      </c>
-      <c r="N96">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96" t="s">
+        <v>10</v>
       </c>
       <c r="O96" t="s">
-        <v>11</v>
-      </c>
-      <c r="P96" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
-        <v>21</v>
-      </c>
-      <c r="B97">
-        <v>0</v>
+      <c r="B97" t="s">
+        <v>40</v>
       </c>
       <c r="C97">
         <v>1</v>
       </c>
       <c r="D97" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E97">
         <v>28.7</v>
@@ -5341,26 +5071,23 @@
       <c r="I97">
         <v>37</v>
       </c>
-      <c r="J97">
+      <c r="J97" s="3">
         <v>2012</v>
       </c>
       <c r="K97" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L97" t="s">
-        <v>26</v>
-      </c>
-      <c r="M97" t="s">
-        <v>16</v>
-      </c>
-      <c r="N97">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="M97">
+        <v>1</v>
+      </c>
+      <c r="N97" t="s">
+        <v>10</v>
       </c>
       <c r="O97" t="s">
-        <v>11</v>
-      </c>
-      <c r="P97" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
